--- a/plot/data/source_data/source_data_fig_3_e.xlsx
+++ b/plot/data/source_data/source_data_fig_3_e.xlsx
@@ -5190,17 +5190,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5221,7 +5222,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>intercept</t>
+          <t>intercept_b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -5236,46 +5237,56 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>n_items</t>
+          <t>n_fit_points</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>n_items_underlying</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fit_data_source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>positive proportional least-squares line through origin</t>
+          <t>ordinary least-squares line with intercept fitted to source x item-type mean points</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>item_rest_discrimination = k * difficulty</t>
+          <t>mean_item_rest_discrimination = k * mean_difficulty + b</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.3911960569246804</v>
+        <v>0.2612869927817942</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>0.0932612485699386</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3046406225401872</v>
+        <v>0.7165043873547383</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0020581834744512</v>
+        <v>0.1091624060703406</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>fig3E_ctt_scatter_item_data.csv from 0612 workflow</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>fig3E_ctt_scatter_summary.csv; grouped by source_true x item_type_group</t>
         </is>
       </c>
     </row>
